--- a/data/trans_bre/IP19C04-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Habitat-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 5,78</t>
+          <t>-7,07; 6,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 1,55</t>
+          <t>-14,0; 0,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 8,14</t>
+          <t>-1,58; 8,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 10,92</t>
+          <t>0,28; 10,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-72,12; 164,7</t>
+          <t>-71,37; 167,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-85,57; 35,42</t>
+          <t>-89,31; 27,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-51,84; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 3,82</t>
+          <t>-6,85; 4,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 9,44</t>
+          <t>-0,26; 9,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 5,99</t>
+          <t>-4,54; 5,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 8,77</t>
+          <t>-1,42; 8,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,25; 82,01</t>
+          <t>-65,08; 100,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 1152,7</t>
+          <t>-15,18; 742,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,88; 181,71</t>
+          <t>-57,93; 225,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 662,75</t>
+          <t>-48,02; 621,95</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 0,35</t>
+          <t>-12,25; 0,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 9,98</t>
+          <t>-4,14; 10,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 5,44</t>
+          <t>-4,67; 5,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 6,5</t>
+          <t>-4,74; 5,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-91,31; 30,24</t>
+          <t>-89,34; 32,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-42,33; 240,95</t>
+          <t>-46,85; 333,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,13; 430,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,95; 341,84</t>
+          <t>-73,82; 261,65</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 7,57</t>
+          <t>-3,66; 8,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 4,47</t>
+          <t>-5,57; 4,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 7,12</t>
+          <t>-3,53; 6,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 1,65</t>
+          <t>-5,37; 2,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,24; 401,07</t>
+          <t>-54,84; 367,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,48; 350,18</t>
+          <t>-84,44; 365,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-57,43; 363,19</t>
+          <t>-63,26; 354,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 267,01</t>
+          <t>-100,0; 330,54</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,87</t>
+          <t>-4,14; 1,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,84</t>
+          <t>-2,24; 3,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,03</t>
+          <t>-1,13; 3,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,14</t>
+          <t>-0,88; 3,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,95; 32,59</t>
+          <t>-47,21; 37,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 83,87</t>
+          <t>-32,55; 80,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 159,24</t>
+          <t>-23,29; 138,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 191,18</t>
+          <t>-25,33; 155,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 6,04</t>
+          <t>-7,21; 6,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 0,97</t>
+          <t>-14,4; 0,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 8,31</t>
+          <t>-1,9; 8,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 10,98</t>
+          <t>0,02; 11,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,37; 167,37</t>
+          <t>-70,94; 197,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-89,31; 27,17</t>
+          <t>-87,42; 28,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,84; —</t>
+          <t>-53,02; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 4,73</t>
+          <t>-7,58; 3,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 9,18</t>
+          <t>0,14; 9,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 5,89</t>
+          <t>-5,03; 5,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 8,45</t>
+          <t>-1,15; 9,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,08; 100,39</t>
+          <t>-68,83; 66,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 742,4</t>
+          <t>-15,06; 841,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,93; 225,2</t>
+          <t>-59,21; 196,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 621,95</t>
+          <t>-45,71; 736,65</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 0,44</t>
+          <t>-11,27; 1,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 10,36</t>
+          <t>-3,88; 10,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 5,16</t>
+          <t>-5,22; 4,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 5,68</t>
+          <t>-4,14; 5,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-89,34; 32,13</t>
+          <t>-89,75; 54,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 333,72</t>
+          <t>-44,33; 276,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-85,13; 430,54</t>
+          <t>-86,91; 304,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,82; 261,65</t>
+          <t>-65,74; 274,82</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 8,03</t>
+          <t>-3,07; 7,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 4,46</t>
+          <t>-5,62; 3,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 6,48</t>
+          <t>-3,45; 6,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 2,0</t>
+          <t>-5,37; 1,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,84; 367,06</t>
+          <t>-57,51; 391,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,44; 365,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,26; 354,02</t>
+          <t>-60,99; 365,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 330,54</t>
+          <t>-100,0; 239,09</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,77</t>
+          <t>-4,3; 1,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,57</t>
+          <t>-2,29; 3,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,84</t>
+          <t>-0,99; 4,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,88</t>
+          <t>-0,87; 3,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 37,09</t>
+          <t>-49,46; 38,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 80,41</t>
+          <t>-31,09; 93,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 138,22</t>
+          <t>-20,74; 158,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 155,73</t>
+          <t>-23,85; 168,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>4,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>219,82%</t>
+          <t>254,48%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 6,32</t>
+          <t>-6,85; 5,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 0,51</t>
+          <t>-14,43; 1,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 8,82</t>
+          <t>-1,82; 8,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 11,65</t>
+          <t>0,26; 11,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-70,94; 197,81</t>
+          <t>-72,12; 164,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,42; 28,77</t>
+          <t>-85,57; 35,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,02; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 3,08</t>
+          <t>-7,48; 3,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 9,0</t>
+          <t>0,05; 9,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 5,9</t>
+          <t>-4,49; 5,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 9,35</t>
+          <t>-1,95; 4,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,83; 66,65</t>
+          <t>-70,25; 82,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 841,77</t>
+          <t>-5,89; 1152,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,21; 196,19</t>
+          <t>-59,88; 181,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,71; 736,65</t>
+          <t>-51,59; 433,09</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 1,07</t>
+          <t>-12,45; 0,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 10,21</t>
+          <t>-3,97; 9,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 4,59</t>
+          <t>-4,52; 5,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 5,62</t>
+          <t>-3,88; 7,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-89,75; 54,22</t>
+          <t>-91,31; 30,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-44,33; 276,53</t>
+          <t>-42,33; 240,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-86,91; 304,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,74; 274,82</t>
+          <t>-64,87; 391,27</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-1,44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-45,28%</t>
+          <t>-44,92%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 7,95</t>
+          <t>-2,98; 7,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 3,97</t>
+          <t>-5,77; 4,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 6,56</t>
+          <t>-2,96; 7,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 1,77</t>
+          <t>-5,41; 1,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,51; 391,13</t>
+          <t>-48,24; 401,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,48; 350,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,99; 365,54</t>
+          <t>-57,43; 363,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 239,09</t>
+          <t>-100,0; 299,08</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,9</t>
+          <t>-4,16; 1,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,86</t>
+          <t>-2,37; 3,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,07</t>
+          <t>-1,23; 4,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,76</t>
+          <t>-0,81; 3,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,46; 38,85</t>
+          <t>-47,95; 32,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 93,91</t>
+          <t>-33,33; 83,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 158,49</t>
+          <t>-25,25; 159,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 168,21</t>
+          <t>-21,22; 171,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C04-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C04-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-6,19</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,52</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-55,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>133,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>254,48%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.5286404217546017</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-6.194233965419674</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.517286916783188</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4.71112157106013</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.07598909193484325</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.5525867158823669</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.337675196972801</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>2.54483107380368</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,85; 5,78</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-14,43; 1,55</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-1,82; 8,14</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,26; 11,14</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-72,12; 164,7</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-85,57; 35,42</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.853809816503574</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-14.42780958436514</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.822146543640428</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.2578838834590241</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7212224207476514</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8557326174257101</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.777250809171</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.5526693151518</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.141455390941596</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11.1414014300572</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.647020154647207</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.3541875865145057</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,61</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,35</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-20,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>152,7%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,51%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>41,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-7,48; 3,82</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 9,44</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,49; 5,99</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,95; 4,82</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-70,25; 82,01</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-5,89; 1152,7</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-59,88; 181,71</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-51,59; 433,09</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.608256812690932</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4.351891436742164</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.018175661342143</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.212855717181146</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.204594108636099</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.527006307549539</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.185126534505706</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.4165182503836758</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,34</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,84</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-59,16%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>29,43%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-7.481513827016737</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.04879134955493864</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.491320004843671</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.947953105634768</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7024513951650129</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.05887884816503955</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5987834247538786</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5158797810901001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-12,45; 0,35</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,97; 9,98</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,52; 5,44</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-3,88; 7,14</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-91,31; 30,24</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-42,33; 240,95</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-64,87; 391,27</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.815695200500824</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9.439360283576084</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.990747217223173</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.823383372017934</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.8200961405995405</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>11.52702027591471</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.817146306224527</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>4.330884693489454</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +811,293 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,44</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>42,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-13,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-44,92%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-5.343247098925005</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.835334842914723</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.2909536906243494</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.269101601249974</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5916467634002738</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.4191902000061809</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.08029662008507847</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.2943432770864111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,98; 7,57</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,77; 4,47</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,96; 7,12</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-5,41; 1,69</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-48,24; 401,07</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-88,48; 350,18</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-57,43; 363,19</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 299,08</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-12.45426215740439</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.965343793079187</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.52295827785677</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.884898463226036</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.9130508274721036</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4232524063384481</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="n">
+        <v>-0.6487245618203709</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.3478494953853536</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>9.978206200925799</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.438124242884831</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.143085997942925</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.3024164008866487</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>2.409519903942355</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="n">
+        <v>3.912672582160108</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.934388643727017</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.5313296293355259</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.616035289231229</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.436808400456505</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.4254454172356167</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1318508172468369</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.4072912728567065</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.4491925688920689</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.98048922677391</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.773527737647311</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.957519497874399</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.413312377431471</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4823595547521093</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.8847528231193482</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5742816875212262</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.567661101298648</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.469630359583771</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.120398071082243</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.685147968486846</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>4.010671860457612</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3.50178116412957</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>3.631879043705029</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2.990805435151253</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-17,44%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>38,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-4,16; 1,87</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,37; 3,84</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,23; 4,03</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,81; 3,58</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-47,95; 32,59</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-33,33; 83,87</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-25,25; 159,24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-21,22; 171,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.235242497071801</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5453006366582815</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.362606974750614</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.216152037853348</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1744109336921355</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.0951364782534824</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.34774439796187</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.3885164540476794</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-4.161618589533731</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.373066499499445</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.231865662351328</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.8130009150433019</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4795010610618686</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3332610507823771</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2525376437117592</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2121568885810222</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.871085736648567</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.836824682774568</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.026638860049214</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.580337996178403</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.3259357150565209</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.8387175221282953</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.592412537469209</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.712822171241668</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1105,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
